--- a/dataset/Tasks.xlsx
+++ b/dataset/Tasks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding\llm\WebAppEval\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75B19A6F-7121-4B93-9D6A-5B048AABD655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814DDBC1-66D1-45D2-B79B-D4DE414FE277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="test" sheetId="6" r:id="rId1"/>
@@ -521,9 +521,6 @@
     <t>Save the product 'Josie Yoga Jacket' to wishlist.</t>
   </si>
   <si>
-    <t>Create a new customer account</t>
-  </si>
-  <si>
     <t>Update the price of the product with SKU 24-WG088 to $15.</t>
   </si>
   <si>
@@ -2293,6 +2290,9 @@
   "match_value": "Lost",
   "description": "Lost opportunities list is displayed"
 }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a new customer account.  </t>
   </si>
 </sst>
 </file>
@@ -3014,19 +3014,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54B76D81-C372-4956-A199-F26C6CB74D23}">
   <dimension ref="A1:J171"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="56" style="13" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" style="12" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" style="12" customWidth="1"/>
-    <col min="5" max="6" width="9.85546875" style="12" customWidth="1"/>
-    <col min="7" max="7" width="21.7109375" style="22" customWidth="1"/>
-    <col min="8" max="8" width="13.7109375" style="22" customWidth="1"/>
-    <col min="9" max="9" width="42.28515625" style="22" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" style="12" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" style="12" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" style="12" customWidth="1"/>
+    <col min="5" max="6" width="9.88671875" style="12" customWidth="1"/>
+    <col min="7" max="7" width="21.6640625" style="22" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" style="22" customWidth="1"/>
+    <col min="9" max="9" width="42.33203125" style="22" customWidth="1"/>
+    <col min="10" max="10" width="11.44140625" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="15" customFormat="1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="15" customFormat="1" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>22</v>
       </c>
@@ -3043,7 +3043,7 @@
         <v>25</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G1" s="21" t="s">
         <v>26</v>
@@ -3058,12 +3058,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="23">
         <v>1</v>
       </c>
       <c r="B2" s="34" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C2" s="30" t="s">
         <v>32</v>
@@ -3084,12 +3084,12 @@
       <c r="I2" s="50"/>
       <c r="J2" s="46"/>
     </row>
-    <row r="3" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="23">
         <v>2</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C3" s="30" t="s">
         <v>69</v>
@@ -3106,16 +3106,16 @@
       <c r="G3" s="50"/>
       <c r="H3" s="50"/>
       <c r="I3" s="50" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J3" s="46"/>
     </row>
-    <row r="4" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="23">
         <v>3</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C4" s="30" t="s">
         <v>32</v>
@@ -3131,17 +3131,17 @@
       </c>
       <c r="G4" s="50"/>
       <c r="H4" s="50" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I4" s="50"/>
       <c r="J4" s="46"/>
     </row>
-    <row r="5" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="23">
         <v>4</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C5" s="30" t="s">
         <v>69</v>
@@ -3162,12 +3162,12 @@
       <c r="I5" s="50"/>
       <c r="J5" s="46"/>
     </row>
-    <row r="6" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="23">
         <v>5</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>134</v>
+        <v>401</v>
       </c>
       <c r="C6" s="30" t="s">
         <v>70</v>
@@ -3184,16 +3184,16 @@
       <c r="G6" s="50"/>
       <c r="H6" s="50"/>
       <c r="I6" s="50" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J6" s="46"/>
     </row>
-    <row r="7" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="23">
         <v>6</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C7" s="30" t="s">
         <v>69</v>
@@ -3214,7 +3214,7 @@
       <c r="I7" s="50"/>
       <c r="J7" s="46"/>
     </row>
-    <row r="8" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="23">
         <v>7</v>
       </c>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="J8" s="46"/>
     </row>
-    <row r="9" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="23">
         <v>8</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C9" s="30" t="s">
         <v>32</v>
@@ -3262,16 +3262,16 @@
       <c r="G9" s="50"/>
       <c r="H9" s="50"/>
       <c r="I9" s="50" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J9" s="46"/>
     </row>
-    <row r="10" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="23">
         <v>9</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C10" s="30" t="s">
         <v>69</v>
@@ -3287,12 +3287,12 @@
       </c>
       <c r="G10" s="50"/>
       <c r="H10" s="50" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="I10" s="50"/>
       <c r="J10" s="46"/>
     </row>
-    <row r="11" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="23">
         <v>10</v>
       </c>
@@ -3314,16 +3314,16 @@
       <c r="G11" s="50"/>
       <c r="H11" s="50"/>
       <c r="I11" s="50" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J11" s="46"/>
     </row>
-    <row r="12" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="23">
         <v>11</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C12" s="30" t="s">
         <v>69</v>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="J12" s="46"/>
     </row>
-    <row r="13" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="23">
         <v>12</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C13" s="30" t="s">
         <v>32</v>
@@ -3370,12 +3370,12 @@
       <c r="I13" s="50"/>
       <c r="J13" s="46"/>
     </row>
-    <row r="14" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="23">
         <v>13</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C14" s="30" t="s">
         <v>32</v>
@@ -3396,12 +3396,12 @@
       <c r="I14" s="50"/>
       <c r="J14" s="46"/>
     </row>
-    <row r="15" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="23">
         <v>14</v>
       </c>
       <c r="B15" s="34" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C15" s="30" t="s">
         <v>69</v>
@@ -3416,18 +3416,18 @@
         <v>9</v>
       </c>
       <c r="G15" s="50" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H15" s="50"/>
       <c r="I15" s="50"/>
       <c r="J15" s="46"/>
     </row>
-    <row r="16" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="23">
         <v>15</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C16" s="30" t="s">
         <v>69</v>
@@ -3446,16 +3446,16 @@
       </c>
       <c r="H16" s="50"/>
       <c r="I16" s="50" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="J16" s="46"/>
     </row>
-    <row r="17" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="23">
         <v>16</v>
       </c>
       <c r="B17" s="35" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C17" s="30" t="s">
         <v>69</v>
@@ -3472,16 +3472,16 @@
       <c r="G17" s="50"/>
       <c r="H17" s="50"/>
       <c r="I17" s="50" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J17" s="46"/>
     </row>
-    <row r="18" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="23">
         <v>17</v>
       </c>
       <c r="B18" s="35" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C18" s="30" t="s">
         <v>69</v>
@@ -3498,16 +3498,16 @@
       <c r="G18" s="50"/>
       <c r="H18" s="50"/>
       <c r="I18" s="50" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J18" s="46"/>
     </row>
-    <row r="19" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="23">
         <v>18</v>
       </c>
       <c r="B19" s="34" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C19" s="30" t="s">
         <v>64</v>
@@ -3522,13 +3522,13 @@
         <v>4</v>
       </c>
       <c r="G19" s="50" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H19" s="50"/>
       <c r="I19" s="50"/>
       <c r="J19" s="46"/>
     </row>
-    <row r="20" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="23">
         <v>19</v>
       </c>
@@ -3550,11 +3550,11 @@
       <c r="G20" s="50"/>
       <c r="H20" s="50"/>
       <c r="I20" s="50" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J20" s="46"/>
     </row>
-    <row r="21" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="23">
         <v>20</v>
       </c>
@@ -3576,11 +3576,11 @@
       <c r="G21" s="50"/>
       <c r="H21" s="50"/>
       <c r="I21" s="50" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J21" s="46"/>
     </row>
-    <row r="22" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="23">
         <v>21</v>
       </c>
@@ -3602,11 +3602,11 @@
       <c r="G22" s="50"/>
       <c r="H22" s="50"/>
       <c r="I22" s="50" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J22" s="46"/>
     </row>
-    <row r="23" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="23">
         <v>22</v>
       </c>
@@ -3628,11 +3628,11 @@
       <c r="G23" s="50"/>
       <c r="H23" s="50"/>
       <c r="I23" s="50" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J23" s="46"/>
     </row>
-    <row r="24" spans="1:10" s="18" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" s="18" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="23">
         <v>23</v>
       </c>
@@ -3654,11 +3654,11 @@
       <c r="G24" s="50"/>
       <c r="H24" s="50"/>
       <c r="I24" s="50" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J24" s="46"/>
     </row>
-    <row r="25" spans="1:10" s="18" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" s="18" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="23">
         <v>24</v>
       </c>
@@ -3680,7 +3680,7 @@
       <c r="G25" s="50"/>
       <c r="H25" s="50"/>
       <c r="I25" s="50" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J25" s="46"/>
     </row>
@@ -3689,7 +3689,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C26" s="30" t="s">
         <v>69</v>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="J26" s="46"/>
     </row>
-    <row r="27" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="23">
         <v>26</v>
       </c>
@@ -3734,11 +3734,11 @@
       <c r="G27" s="50"/>
       <c r="H27" s="50"/>
       <c r="I27" s="50" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J27" s="46"/>
     </row>
-    <row r="28" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="23">
         <v>27</v>
       </c>
@@ -3760,11 +3760,11 @@
       <c r="G28" s="50"/>
       <c r="H28" s="50"/>
       <c r="I28" s="50" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J28" s="46"/>
     </row>
-    <row r="29" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="23">
         <v>28</v>
       </c>
@@ -3786,16 +3786,16 @@
       <c r="G29" s="50"/>
       <c r="H29" s="50"/>
       <c r="I29" s="50" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J29" s="46"/>
     </row>
-    <row r="30" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="23">
         <v>29</v>
       </c>
       <c r="B30" s="35" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C30" s="30" t="s">
         <v>69</v>
@@ -3812,16 +3812,16 @@
       <c r="G30" s="50"/>
       <c r="H30" s="50"/>
       <c r="I30" s="50" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J30" s="46"/>
     </row>
-    <row r="31" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="23">
         <v>30</v>
       </c>
       <c r="B31" s="34" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C31" s="30" t="s">
         <v>69</v>
@@ -3838,16 +3838,16 @@
       <c r="G31" s="52"/>
       <c r="H31" s="52"/>
       <c r="I31" s="50" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J31" s="46"/>
     </row>
-    <row r="32" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="23">
         <v>31</v>
       </c>
       <c r="B32" s="35" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C32" s="30" t="s">
         <v>69</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="J32" s="46"/>
     </row>
-    <row r="33" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="23">
         <v>32</v>
       </c>
       <c r="B33" s="35" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C33" s="30" t="s">
         <v>69</v>
@@ -3890,11 +3890,11 @@
       <c r="G33" s="50"/>
       <c r="H33" s="50"/>
       <c r="I33" s="50" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J33" s="46"/>
     </row>
-    <row r="34" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="23">
         <v>33</v>
       </c>
@@ -3916,16 +3916,16 @@
       <c r="G34" s="50"/>
       <c r="H34" s="50"/>
       <c r="I34" s="50" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J34" s="46"/>
     </row>
-    <row r="35" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="23">
         <v>34</v>
       </c>
       <c r="B35" s="35" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C35" s="30" t="s">
         <v>69</v>
@@ -3942,7 +3942,7 @@
       <c r="G35" s="50"/>
       <c r="H35" s="50"/>
       <c r="I35" s="50" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J35" s="46"/>
     </row>
@@ -3951,7 +3951,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="39" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C36" s="30" t="s">
         <v>69</v>
@@ -3968,11 +3968,11 @@
       <c r="G36" s="50"/>
       <c r="H36" s="50"/>
       <c r="I36" s="50" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J36" s="46"/>
     </row>
-    <row r="37" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="23">
         <v>36</v>
       </c>
@@ -3998,12 +3998,12 @@
       </c>
       <c r="J37" s="46"/>
     </row>
-    <row r="38" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="23">
         <v>37</v>
       </c>
       <c r="B38" s="35" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C38" s="30" t="s">
         <v>69</v>
@@ -4020,11 +4020,11 @@
       <c r="G38" s="50"/>
       <c r="H38" s="50"/>
       <c r="I38" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J38" s="46"/>
     </row>
-    <row r="39" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="23">
         <v>38</v>
       </c>
@@ -4046,11 +4046,11 @@
       <c r="G39" s="50"/>
       <c r="H39" s="50"/>
       <c r="I39" s="50" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J39" s="46"/>
     </row>
-    <row r="40" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="23">
         <v>39</v>
       </c>
@@ -4072,11 +4072,11 @@
       <c r="G40" s="50"/>
       <c r="H40" s="50"/>
       <c r="I40" s="50" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J40" s="46"/>
     </row>
-    <row r="41" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="23">
         <v>40</v>
       </c>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="J41" s="46"/>
     </row>
-    <row r="42" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="23">
         <v>41</v>
       </c>
@@ -4124,11 +4124,11 @@
       <c r="G42" s="50"/>
       <c r="H42" s="50"/>
       <c r="I42" s="50" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J42" s="46"/>
     </row>
-    <row r="43" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="23">
         <v>42</v>
       </c>
@@ -4150,16 +4150,16 @@
       <c r="G43" s="50"/>
       <c r="H43" s="50"/>
       <c r="I43" s="50" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J43" s="46"/>
     </row>
-    <row r="44" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="23">
         <v>43</v>
       </c>
       <c r="B44" s="35" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C44" s="30" t="s">
         <v>69</v>
@@ -4176,11 +4176,11 @@
       <c r="G44" s="50"/>
       <c r="H44" s="50"/>
       <c r="I44" s="50" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J44" s="46"/>
     </row>
-    <row r="45" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="23">
         <v>44</v>
       </c>
@@ -4202,11 +4202,11 @@
       <c r="G45" s="50"/>
       <c r="H45" s="50"/>
       <c r="I45" s="50" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J45" s="46"/>
     </row>
-    <row r="46" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="23">
         <v>45</v>
       </c>
@@ -4228,11 +4228,11 @@
       <c r="G46" s="50"/>
       <c r="H46" s="50"/>
       <c r="I46" s="50" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="J46" s="46"/>
     </row>
-    <row r="47" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="23">
         <v>46</v>
       </c>
@@ -4254,11 +4254,11 @@
       <c r="G47" s="50"/>
       <c r="H47" s="50"/>
       <c r="I47" s="50" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J47" s="46"/>
     </row>
-    <row r="48" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="23">
         <v>47</v>
       </c>
@@ -4280,11 +4280,11 @@
       <c r="G48" s="50"/>
       <c r="H48" s="50"/>
       <c r="I48" s="50" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J48" s="46"/>
     </row>
-    <row r="49" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="23">
         <v>48</v>
       </c>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="J49" s="46"/>
     </row>
-    <row r="50" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="23">
         <v>49</v>
       </c>
@@ -4332,11 +4332,11 @@
       <c r="G50" s="50"/>
       <c r="H50" s="50"/>
       <c r="I50" s="50" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J50" s="46"/>
     </row>
-    <row r="51" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="23">
         <v>50</v>
       </c>
@@ -4358,11 +4358,11 @@
       <c r="G51" s="50"/>
       <c r="H51" s="50"/>
       <c r="I51" s="50" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J51" s="46"/>
     </row>
-    <row r="52" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="23">
         <v>51</v>
       </c>
@@ -4384,11 +4384,11 @@
       <c r="G52" s="50"/>
       <c r="H52" s="50"/>
       <c r="I52" s="50" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J52" s="46"/>
     </row>
-    <row r="53" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="23">
         <v>52</v>
       </c>
@@ -4410,11 +4410,11 @@
       <c r="G53" s="50"/>
       <c r="H53" s="50"/>
       <c r="I53" s="50" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J53" s="46"/>
     </row>
-    <row r="54" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="23">
         <v>53</v>
       </c>
@@ -4436,11 +4436,11 @@
       <c r="G54" s="50"/>
       <c r="H54" s="50"/>
       <c r="I54" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="J54" s="46"/>
     </row>
-    <row r="55" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="23">
         <v>54</v>
       </c>
@@ -4462,11 +4462,11 @@
       <c r="G55" s="50"/>
       <c r="H55" s="50"/>
       <c r="I55" s="50" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J55" s="46"/>
     </row>
-    <row r="56" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="23">
         <v>55</v>
       </c>
@@ -4488,11 +4488,11 @@
       <c r="G56" s="50"/>
       <c r="H56" s="50"/>
       <c r="I56" s="50" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J56" s="46"/>
     </row>
-    <row r="57" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="23">
         <v>56</v>
       </c>
@@ -4514,11 +4514,11 @@
       <c r="G57" s="50"/>
       <c r="H57" s="50"/>
       <c r="I57" s="50" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="J57" s="46"/>
     </row>
-    <row r="58" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="23">
         <v>57</v>
       </c>
@@ -4540,11 +4540,11 @@
       <c r="G58" s="50"/>
       <c r="H58" s="50"/>
       <c r="I58" s="50" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="J58" s="46"/>
     </row>
-    <row r="59" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="23">
         <v>58</v>
       </c>
@@ -4566,11 +4566,11 @@
       <c r="G59" s="50"/>
       <c r="H59" s="50"/>
       <c r="I59" s="50" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J59" s="46"/>
     </row>
-    <row r="60" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="23">
         <v>59</v>
       </c>
@@ -4592,11 +4592,11 @@
       <c r="G60" s="50"/>
       <c r="H60" s="50"/>
       <c r="I60" s="50" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J60" s="46"/>
     </row>
-    <row r="61" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="23">
         <v>60</v>
       </c>
@@ -4618,11 +4618,11 @@
       <c r="G61" s="50"/>
       <c r="H61" s="50"/>
       <c r="I61" s="50" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="J61" s="46"/>
     </row>
-    <row r="62" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="23">
         <v>61</v>
       </c>
@@ -4644,11 +4644,11 @@
       <c r="G62" s="50"/>
       <c r="H62" s="50"/>
       <c r="I62" s="50" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J62" s="46"/>
     </row>
-    <row r="63" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="23">
         <v>62</v>
       </c>
@@ -4670,11 +4670,11 @@
       <c r="G63" s="50"/>
       <c r="H63" s="50"/>
       <c r="I63" s="50" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="J63" s="46"/>
     </row>
-    <row r="64" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="23">
         <v>63</v>
       </c>
@@ -4696,11 +4696,11 @@
       <c r="G64" s="50"/>
       <c r="H64" s="50"/>
       <c r="I64" s="50" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J64" s="46"/>
     </row>
-    <row r="65" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="23">
         <v>64</v>
       </c>
@@ -4722,11 +4722,11 @@
       <c r="G65" s="50"/>
       <c r="H65" s="50"/>
       <c r="I65" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J65" s="46"/>
     </row>
-    <row r="66" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="23">
         <v>65</v>
       </c>
@@ -4748,11 +4748,11 @@
       <c r="G66" s="50"/>
       <c r="H66" s="50"/>
       <c r="I66" s="50" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J66" s="46"/>
     </row>
-    <row r="67" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="23">
         <v>66</v>
       </c>
@@ -4774,11 +4774,11 @@
       <c r="G67" s="50"/>
       <c r="H67" s="50"/>
       <c r="I67" s="50" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J67" s="46"/>
     </row>
-    <row r="68" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="23">
         <v>67</v>
       </c>
@@ -4800,11 +4800,11 @@
       <c r="G68" s="50"/>
       <c r="H68" s="50"/>
       <c r="I68" s="50" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="J68" s="46"/>
     </row>
-    <row r="69" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="23">
         <v>68</v>
       </c>
@@ -4826,11 +4826,11 @@
       <c r="G69" s="50"/>
       <c r="H69" s="50"/>
       <c r="I69" s="50" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="J69" s="46"/>
     </row>
-    <row r="70" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="23">
         <v>69</v>
       </c>
@@ -4852,11 +4852,11 @@
       <c r="G70" s="50"/>
       <c r="H70" s="50"/>
       <c r="I70" s="50" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J70" s="46"/>
     </row>
-    <row r="71" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="23">
         <v>70</v>
       </c>
@@ -4878,11 +4878,11 @@
       <c r="G71" s="50"/>
       <c r="H71" s="50"/>
       <c r="I71" s="50" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="J71" s="46"/>
     </row>
-    <row r="72" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="23">
         <v>71</v>
       </c>
@@ -4904,16 +4904,16 @@
       <c r="G72" s="50"/>
       <c r="H72" s="50"/>
       <c r="I72" s="50" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="J72" s="46"/>
     </row>
-    <row r="73" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="23">
         <v>72</v>
       </c>
       <c r="B73" s="34" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C73" s="30" t="s">
         <v>69</v>
@@ -4928,13 +4928,13 @@
         <v>8</v>
       </c>
       <c r="G73" s="50" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H73" s="50"/>
       <c r="I73" s="50"/>
       <c r="J73" s="46"/>
     </row>
-    <row r="74" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="23">
         <v>73</v>
       </c>
@@ -4956,11 +4956,11 @@
       <c r="G74" s="50"/>
       <c r="H74" s="50"/>
       <c r="I74" s="50" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J74" s="46"/>
     </row>
-    <row r="75" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="23">
         <v>74</v>
       </c>
@@ -4982,11 +4982,11 @@
       <c r="G75" s="50"/>
       <c r="H75" s="50"/>
       <c r="I75" s="50" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J75" s="46"/>
     </row>
-    <row r="76" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="23">
         <v>75</v>
       </c>
@@ -5008,11 +5008,11 @@
       <c r="G76" s="50"/>
       <c r="H76" s="50"/>
       <c r="I76" s="50" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J76" s="46"/>
     </row>
-    <row r="77" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="23">
         <v>76</v>
       </c>
@@ -5034,11 +5034,11 @@
       <c r="G77" s="50"/>
       <c r="H77" s="50"/>
       <c r="I77" s="50" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J77" s="46"/>
     </row>
-    <row r="78" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="23">
         <v>77</v>
       </c>
@@ -5060,16 +5060,16 @@
       <c r="G78" s="50"/>
       <c r="H78" s="50"/>
       <c r="I78" s="50" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J78" s="46"/>
     </row>
-    <row r="79" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="23">
         <v>78</v>
       </c>
       <c r="B79" s="35" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C79" s="30" t="s">
         <v>69</v>
@@ -5086,11 +5086,11 @@
       <c r="G79" s="50"/>
       <c r="H79" s="50"/>
       <c r="I79" s="50" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="J79" s="46"/>
     </row>
-    <row r="80" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="23">
         <v>79</v>
       </c>
@@ -5112,16 +5112,16 @@
       <c r="G80" s="50"/>
       <c r="H80" s="50"/>
       <c r="I80" s="50" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J80" s="46"/>
     </row>
-    <row r="81" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="23">
         <v>80</v>
       </c>
       <c r="B81" s="35" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C81" s="30" t="s">
         <v>69</v>
@@ -5138,11 +5138,11 @@
       <c r="G81" s="50"/>
       <c r="H81" s="50"/>
       <c r="I81" s="50" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J81" s="46"/>
     </row>
-    <row r="82" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="23">
         <v>81</v>
       </c>
@@ -5164,11 +5164,11 @@
       <c r="G82" s="50"/>
       <c r="H82" s="50"/>
       <c r="I82" s="50" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="J82" s="46"/>
     </row>
-    <row r="83" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="23">
         <v>82</v>
       </c>
@@ -5190,11 +5190,11 @@
       <c r="G83" s="50"/>
       <c r="H83" s="50"/>
       <c r="I83" s="50" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J83" s="46"/>
     </row>
-    <row r="84" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="23">
         <v>83</v>
       </c>
@@ -5216,11 +5216,11 @@
       <c r="G84" s="50"/>
       <c r="H84" s="50"/>
       <c r="I84" s="50" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="J84" s="46"/>
     </row>
-    <row r="85" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="23">
         <v>84</v>
       </c>
@@ -5242,16 +5242,16 @@
       <c r="G85" s="50"/>
       <c r="H85" s="50"/>
       <c r="I85" s="50" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="J85" s="46"/>
     </row>
-    <row r="86" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="23">
         <v>85</v>
       </c>
       <c r="B86" s="35" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C86" s="30" t="s">
         <v>69</v>
@@ -5268,11 +5268,11 @@
       <c r="G86" s="50"/>
       <c r="H86" s="50"/>
       <c r="I86" s="50" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J86" s="46"/>
     </row>
-    <row r="87" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="23">
         <v>86</v>
       </c>
@@ -5294,16 +5294,16 @@
       <c r="G87" s="50"/>
       <c r="H87" s="50"/>
       <c r="I87" s="50" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="J87" s="46"/>
     </row>
-    <row r="88" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="23">
         <v>87</v>
       </c>
       <c r="B88" s="35" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C88" s="30" t="s">
         <v>69</v>
@@ -5320,11 +5320,11 @@
       <c r="G88" s="50"/>
       <c r="H88" s="50"/>
       <c r="I88" s="50" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="J88" s="46"/>
     </row>
-    <row r="89" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="23">
         <v>88</v>
       </c>
@@ -5346,16 +5346,16 @@
       <c r="G89" s="50"/>
       <c r="H89" s="50"/>
       <c r="I89" s="50" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J89" s="46"/>
     </row>
-    <row r="90" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="23">
         <v>89</v>
       </c>
       <c r="B90" s="34" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C90" s="30" t="s">
         <v>69</v>
@@ -5370,18 +5370,18 @@
         <v>4</v>
       </c>
       <c r="G90" s="50" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H90" s="50"/>
       <c r="I90" s="50"/>
       <c r="J90" s="46"/>
     </row>
-    <row r="91" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="23">
         <v>90</v>
       </c>
       <c r="B91" s="34" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C91" s="30" t="s">
         <v>32</v>
@@ -5402,12 +5402,12 @@
       <c r="I91" s="50"/>
       <c r="J91" s="46"/>
     </row>
-    <row r="92" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="23">
         <v>91</v>
       </c>
       <c r="B92" s="34" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C92" s="30" t="s">
         <v>32</v>
@@ -5428,12 +5428,12 @@
       <c r="I92" s="50"/>
       <c r="J92" s="46"/>
     </row>
-    <row r="93" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="23">
         <v>92</v>
       </c>
       <c r="B93" s="34" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C93" s="30" t="s">
         <v>32</v>
@@ -5454,12 +5454,12 @@
       <c r="I93" s="50"/>
       <c r="J93" s="46"/>
     </row>
-    <row r="94" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="23">
         <v>93</v>
       </c>
       <c r="B94" s="34" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C94" s="30" t="s">
         <v>32</v>
@@ -5474,18 +5474,18 @@
         <v>6</v>
       </c>
       <c r="G94" s="50" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H94" s="50"/>
       <c r="I94" s="50"/>
       <c r="J94" s="46"/>
     </row>
-    <row r="95" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="23">
         <v>94</v>
       </c>
       <c r="B95" s="34" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C95" s="30" t="s">
         <v>32</v>
@@ -5506,12 +5506,12 @@
       <c r="I95" s="50"/>
       <c r="J95" s="46"/>
     </row>
-    <row r="96" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="23">
         <v>95</v>
       </c>
       <c r="B96" s="34" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C96" s="30" t="s">
         <v>32</v>
@@ -5528,16 +5528,16 @@
       <c r="G96" s="50"/>
       <c r="H96" s="50"/>
       <c r="I96" s="50" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J96" s="46"/>
     </row>
-    <row r="97" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="23">
         <v>96</v>
       </c>
       <c r="B97" s="34" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C97" s="30" t="s">
         <v>32</v>
@@ -5552,13 +5552,13 @@
         <v>4</v>
       </c>
       <c r="G97" s="50" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H97" s="50"/>
       <c r="I97" s="50"/>
       <c r="J97" s="46"/>
     </row>
-    <row r="98" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="23">
         <v>97</v>
       </c>
@@ -5580,11 +5580,11 @@
       <c r="G98" s="50"/>
       <c r="H98" s="50"/>
       <c r="I98" s="50" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="J98" s="46"/>
     </row>
-    <row r="99" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="23">
         <v>98</v>
       </c>
@@ -5606,16 +5606,16 @@
       <c r="G99" s="50"/>
       <c r="H99" s="50"/>
       <c r="I99" s="50" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="J99" s="46"/>
     </row>
-    <row r="100" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="23">
         <v>99</v>
       </c>
       <c r="B100" s="34" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C100" s="30" t="s">
         <v>69</v>
@@ -5630,13 +5630,13 @@
         <v>6</v>
       </c>
       <c r="G100" s="50" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H100" s="50"/>
       <c r="I100" s="50"/>
       <c r="J100" s="46"/>
     </row>
-    <row r="101" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="23">
         <v>100</v>
       </c>
@@ -5658,16 +5658,16 @@
       <c r="G101" s="55"/>
       <c r="H101" s="55"/>
       <c r="I101" s="50" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="J101" s="46"/>
     </row>
-    <row r="102" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="23">
         <v>101</v>
       </c>
       <c r="B102" s="35" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C102" s="30" t="s">
         <v>69</v>
@@ -5684,16 +5684,16 @@
       <c r="G102" s="55"/>
       <c r="H102" s="55"/>
       <c r="I102" s="55" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J102" s="46"/>
     </row>
-    <row r="103" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="23">
         <v>102</v>
       </c>
       <c r="B103" s="27" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C103" s="40" t="s">
         <v>70</v>
@@ -5710,16 +5710,16 @@
       <c r="G103" s="42"/>
       <c r="H103" s="42"/>
       <c r="I103" s="42" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J103" s="46"/>
     </row>
-    <row r="104" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="23">
         <v>103</v>
       </c>
       <c r="B104" s="35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C104" s="30" t="s">
         <v>69</v>
@@ -5736,16 +5736,16 @@
       <c r="G104" s="55"/>
       <c r="H104" s="55"/>
       <c r="I104" s="55" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J104" s="46"/>
     </row>
-    <row r="105" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="23">
         <v>104</v>
       </c>
       <c r="B105" s="35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C105" s="30" t="s">
         <v>69</v>
@@ -5762,16 +5762,16 @@
       <c r="G105" s="55"/>
       <c r="H105" s="55"/>
       <c r="I105" s="55" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J105" s="46"/>
     </row>
-    <row r="106" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="23">
         <v>105</v>
       </c>
       <c r="B106" s="35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C106" s="30" t="s">
         <v>69</v>
@@ -5787,17 +5787,17 @@
       </c>
       <c r="G106" s="55"/>
       <c r="H106" s="55" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I106" s="55"/>
       <c r="J106" s="46"/>
     </row>
-    <row r="107" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="23">
         <v>106</v>
       </c>
       <c r="B107" s="35" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C107" s="30" t="s">
         <v>69</v>
@@ -5813,17 +5813,17 @@
       </c>
       <c r="G107" s="55"/>
       <c r="H107" s="55" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I107" s="55"/>
       <c r="J107" s="46"/>
     </row>
-    <row r="108" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="23">
         <v>107</v>
       </c>
       <c r="B108" s="36" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C108" s="30" t="s">
         <v>69</v>
@@ -5840,16 +5840,16 @@
       <c r="G108" s="55"/>
       <c r="H108" s="55"/>
       <c r="I108" s="55" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="J108" s="46"/>
     </row>
-    <row r="109" spans="1:10" s="19" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" s="19" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="23">
         <v>108</v>
       </c>
       <c r="B109" s="35" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C109" s="30" t="s">
         <v>32</v>
@@ -5865,17 +5865,17 @@
       </c>
       <c r="G109" s="55"/>
       <c r="H109" s="55" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I109" s="55"/>
       <c r="J109" s="47"/>
     </row>
-    <row r="110" spans="1:10" s="19" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" s="19" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="23">
         <v>109</v>
       </c>
       <c r="B110" s="34" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C110" s="31" t="s">
         <v>32</v>
@@ -5892,16 +5892,16 @@
       <c r="G110" s="55"/>
       <c r="H110" s="55"/>
       <c r="I110" s="55" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J110" s="47"/>
     </row>
-    <row r="111" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="23">
         <v>110</v>
       </c>
       <c r="B111" s="36" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C111" s="32" t="s">
         <v>32</v>
@@ -5917,17 +5917,17 @@
       </c>
       <c r="G111" s="55"/>
       <c r="H111" s="55" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I111" s="55"/>
       <c r="J111" s="46"/>
     </row>
-    <row r="112" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="23">
         <v>111</v>
       </c>
       <c r="B112" s="35" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C112" s="33" t="s">
         <v>32</v>
@@ -5943,19 +5943,19 @@
       </c>
       <c r="G112" s="55"/>
       <c r="H112" s="55" t="s">
+        <v>195</v>
+      </c>
+      <c r="I112" s="55" t="s">
         <v>196</v>
       </c>
-      <c r="I112" s="55" t="s">
-        <v>197</v>
-      </c>
       <c r="J112" s="46"/>
     </row>
-    <row r="113" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="23">
         <v>112</v>
       </c>
       <c r="B113" s="35" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C113" s="33" t="s">
         <v>69</v>
@@ -5972,16 +5972,16 @@
       <c r="G113" s="55"/>
       <c r="H113" s="55"/>
       <c r="I113" s="55" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J113" s="46"/>
     </row>
-    <row r="114" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="23">
         <v>113</v>
       </c>
       <c r="B114" s="36" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C114" s="33" t="s">
         <v>70</v>
@@ -5998,16 +5998,16 @@
       <c r="G114" s="55"/>
       <c r="H114" s="55"/>
       <c r="I114" s="55" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J114" s="46"/>
     </row>
-    <row r="115" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="23">
         <v>114</v>
       </c>
       <c r="B115" s="36" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C115" s="33" t="s">
         <v>70</v>
@@ -6024,16 +6024,16 @@
       <c r="G115" s="55"/>
       <c r="H115" s="55"/>
       <c r="I115" s="55" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J115" s="46"/>
     </row>
-    <row r="116" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="23">
         <v>115</v>
       </c>
       <c r="B116" s="35" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C116" s="33" t="s">
         <v>69</v>
@@ -6050,16 +6050,16 @@
       <c r="G116" s="55"/>
       <c r="H116" s="55"/>
       <c r="I116" s="55" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J116" s="46"/>
     </row>
-    <row r="117" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="23">
         <v>116</v>
       </c>
       <c r="B117" s="35" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C117" s="33" t="s">
         <v>32</v>
@@ -6076,16 +6076,16 @@
       <c r="G117" s="55"/>
       <c r="H117" s="55"/>
       <c r="I117" s="55" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J117" s="46"/>
     </row>
-    <row r="118" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="23">
         <v>117</v>
       </c>
       <c r="B118" s="35" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C118" s="33" t="s">
         <v>32</v>
@@ -6102,16 +6102,16 @@
       <c r="G118" s="55"/>
       <c r="H118" s="55"/>
       <c r="I118" s="55" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J118" s="46"/>
     </row>
-    <row r="119" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="23">
         <v>118</v>
       </c>
       <c r="B119" s="35" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C119" s="33" t="s">
         <v>32</v>
@@ -6127,19 +6127,19 @@
       </c>
       <c r="G119" s="55"/>
       <c r="H119" s="55" t="s">
+        <v>206</v>
+      </c>
+      <c r="I119" s="55" t="s">
         <v>207</v>
       </c>
-      <c r="I119" s="55" t="s">
-        <v>208</v>
-      </c>
       <c r="J119" s="46"/>
     </row>
-    <row r="120" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="23">
         <v>119</v>
       </c>
       <c r="B120" s="35" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C120" s="30" t="s">
         <v>69</v>
@@ -6156,16 +6156,16 @@
       <c r="G120" s="55"/>
       <c r="H120" s="55"/>
       <c r="I120" s="55" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J120" s="46"/>
     </row>
-    <row r="121" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="23">
         <v>120</v>
       </c>
       <c r="B121" s="35" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C121" s="30" t="s">
         <v>69</v>
@@ -6181,19 +6181,19 @@
       </c>
       <c r="G121" s="55"/>
       <c r="H121" s="55" t="s">
+        <v>208</v>
+      </c>
+      <c r="I121" s="55" t="s">
         <v>209</v>
       </c>
-      <c r="I121" s="55" t="s">
-        <v>210</v>
-      </c>
       <c r="J121" s="46"/>
     </row>
-    <row r="122" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="23">
         <v>121</v>
       </c>
       <c r="B122" s="35" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C122" s="30" t="s">
         <v>69</v>
@@ -6210,16 +6210,16 @@
       <c r="G122" s="55"/>
       <c r="H122" s="55"/>
       <c r="I122" s="55" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J122" s="46"/>
     </row>
-    <row r="123" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="23">
         <v>122</v>
       </c>
       <c r="B123" s="35" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C123" s="30" t="s">
         <v>69</v>
@@ -6236,16 +6236,16 @@
       <c r="G123" s="55"/>
       <c r="H123" s="55"/>
       <c r="I123" s="55" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J123" s="48"/>
     </row>
-    <row r="124" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="23">
         <v>123</v>
       </c>
       <c r="B124" s="34" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C124" s="33" t="s">
         <v>70</v>
@@ -6262,16 +6262,16 @@
       <c r="G124" s="55"/>
       <c r="H124" s="55"/>
       <c r="I124" s="55" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J124" s="48"/>
     </row>
-    <row r="125" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="23">
         <v>124</v>
       </c>
       <c r="B125" s="34" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C125" s="33" t="s">
         <v>70</v>
@@ -6288,16 +6288,16 @@
       <c r="G125" s="55"/>
       <c r="H125" s="55"/>
       <c r="I125" s="55" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J125" s="48"/>
     </row>
-    <row r="126" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="23">
         <v>125</v>
       </c>
       <c r="B126" s="27" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C126" s="33" t="s">
         <v>69</v>
@@ -6314,7 +6314,7 @@
       <c r="G126" s="55"/>
       <c r="H126" s="55"/>
       <c r="I126" s="55" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J126" s="48"/>
     </row>
@@ -6323,7 +6323,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="38" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C127" s="33" t="s">
         <v>70</v>
@@ -6340,7 +6340,7 @@
       <c r="G127" s="55"/>
       <c r="H127" s="55"/>
       <c r="I127" s="55" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J127" s="48"/>
     </row>
@@ -6349,7 +6349,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="43" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C128" s="33" t="s">
         <v>70</v>
@@ -6366,7 +6366,7 @@
       <c r="G128" s="55"/>
       <c r="H128" s="55"/>
       <c r="I128" s="55" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J128" s="48"/>
     </row>
@@ -6375,7 +6375,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C129" s="33" t="s">
         <v>32</v>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="G129" s="55"/>
       <c r="H129" s="55" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I129" s="55"/>
       <c r="J129" s="48"/>
@@ -6401,7 +6401,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="39" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C130" s="33" t="s">
         <v>69</v>
@@ -6418,7 +6418,7 @@
       <c r="G130" s="55"/>
       <c r="H130" s="55"/>
       <c r="I130" s="55" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J130" s="48"/>
     </row>
@@ -6427,7 +6427,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="28" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C131" s="33" t="s">
         <v>69</v>
@@ -6444,7 +6444,7 @@
       <c r="G131" s="55"/>
       <c r="H131" s="55"/>
       <c r="I131" s="55" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J131" s="48"/>
     </row>
@@ -6453,7 +6453,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="44" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C132" s="33" t="s">
         <v>69</v>
@@ -6470,7 +6470,7 @@
       <c r="G132" s="55"/>
       <c r="H132" s="55"/>
       <c r="I132" s="55" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J132" s="48"/>
     </row>
@@ -6479,7 +6479,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="28" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C133" s="33" t="s">
         <v>32</v>
@@ -6496,7 +6496,7 @@
       <c r="G133" s="55"/>
       <c r="H133" s="55"/>
       <c r="I133" s="55" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J133" s="48"/>
     </row>
@@ -6505,7 +6505,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="44" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C134" s="33" t="s">
         <v>69</v>
@@ -6522,16 +6522,16 @@
       <c r="G134" s="55"/>
       <c r="H134" s="55"/>
       <c r="I134" s="55" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J134" s="48"/>
     </row>
-    <row r="135" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="23">
         <v>134</v>
       </c>
       <c r="B135" s="45" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C135" s="33" t="s">
         <v>69</v>
@@ -6548,16 +6548,16 @@
       <c r="G135" s="55"/>
       <c r="H135" s="55"/>
       <c r="I135" s="55" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J135" s="48"/>
     </row>
-    <row r="136" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="23">
         <v>135</v>
       </c>
       <c r="B136" s="45" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C136" s="33" t="s">
         <v>70</v>
@@ -6574,7 +6574,7 @@
       <c r="G136" s="55"/>
       <c r="H136" s="55"/>
       <c r="I136" s="55" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J136" s="48"/>
     </row>
@@ -6583,7 +6583,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="44" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C137" s="33" t="s">
         <v>69</v>
@@ -6600,7 +6600,7 @@
       <c r="G137" s="55"/>
       <c r="H137" s="55"/>
       <c r="I137" s="55" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J137" s="48"/>
     </row>
@@ -6609,7 +6609,7 @@
         <v>137</v>
       </c>
       <c r="B138" s="44" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C138" s="33" t="s">
         <v>70</v>
@@ -6626,7 +6626,7 @@
       <c r="G138" s="55"/>
       <c r="H138" s="55"/>
       <c r="I138" s="55" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J138" s="48"/>
     </row>
@@ -6635,7 +6635,7 @@
         <v>138</v>
       </c>
       <c r="B139" s="44" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C139" s="33" t="s">
         <v>69</v>
@@ -6652,16 +6652,16 @@
       <c r="G139" s="55"/>
       <c r="H139" s="55"/>
       <c r="I139" s="55" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J139" s="48"/>
     </row>
-    <row r="140" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="23">
         <v>139</v>
       </c>
       <c r="B140" s="34" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C140" s="33" t="s">
         <v>69</v>
@@ -6678,7 +6678,7 @@
       <c r="G140" s="59"/>
       <c r="H140" s="59"/>
       <c r="I140" s="59" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J140" s="48"/>
     </row>
@@ -6687,7 +6687,7 @@
         <v>140</v>
       </c>
       <c r="B141" s="44" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C141" s="33" t="s">
         <v>69</v>
@@ -6704,7 +6704,7 @@
       <c r="G141" s="55"/>
       <c r="H141" s="55"/>
       <c r="I141" s="55" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J141" s="48"/>
     </row>
@@ -6713,7 +6713,7 @@
         <v>141</v>
       </c>
       <c r="B142" s="44" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C142" s="33" t="s">
         <v>69</v>
@@ -6730,16 +6730,16 @@
       <c r="G142" s="55"/>
       <c r="H142" s="55"/>
       <c r="I142" s="55" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J142" s="48"/>
     </row>
-    <row r="143" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="23">
         <v>142</v>
       </c>
       <c r="B143" s="45" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C143" s="33" t="s">
         <v>69</v>
@@ -6756,16 +6756,16 @@
       <c r="G143" s="55"/>
       <c r="H143" s="55"/>
       <c r="I143" s="55" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J143" s="48"/>
     </row>
-    <row r="144" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="23">
         <v>143</v>
       </c>
       <c r="B144" s="35" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C144" s="33" t="s">
         <v>69</v>
@@ -6782,16 +6782,16 @@
       <c r="G144" s="55"/>
       <c r="H144" s="55"/>
       <c r="I144" s="55" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J144" s="48"/>
     </row>
-    <row r="145" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="23">
         <v>144</v>
       </c>
       <c r="B145" s="45" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C145" s="33" t="s">
         <v>69</v>
@@ -6808,16 +6808,16 @@
       <c r="G145" s="55"/>
       <c r="H145" s="55"/>
       <c r="I145" s="55" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J145" s="48"/>
     </row>
-    <row r="146" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="23">
         <v>145</v>
       </c>
       <c r="B146" s="34" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C146" s="33" t="s">
         <v>69</v>
@@ -6834,16 +6834,16 @@
       <c r="G146" s="55"/>
       <c r="H146" s="55"/>
       <c r="I146" s="55" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J146" s="48"/>
     </row>
-    <row r="147" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="23">
         <v>146</v>
       </c>
       <c r="B147" s="45" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C147" s="33" t="s">
         <v>69</v>
@@ -6860,16 +6860,16 @@
       <c r="G147" s="55"/>
       <c r="H147" s="55"/>
       <c r="I147" s="55" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J147" s="48"/>
     </row>
-    <row r="148" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="23">
         <v>147</v>
       </c>
       <c r="B148" s="45" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C148" s="33" t="s">
         <v>69</v>
@@ -6886,16 +6886,16 @@
       <c r="G148" s="55"/>
       <c r="H148" s="55"/>
       <c r="I148" s="55" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J148" s="48"/>
     </row>
-    <row r="149" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="23">
         <v>148</v>
       </c>
       <c r="B149" s="45" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C149" s="33" t="s">
         <v>69</v>
@@ -6912,16 +6912,16 @@
       <c r="G149" s="55"/>
       <c r="H149" s="55"/>
       <c r="I149" s="55" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J149" s="48"/>
     </row>
-    <row r="150" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="23">
         <v>149</v>
       </c>
       <c r="B150" s="45" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C150" s="33" t="s">
         <v>69</v>
@@ -6938,16 +6938,16 @@
       <c r="G150" s="55"/>
       <c r="H150" s="55"/>
       <c r="I150" s="55" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J150" s="48"/>
     </row>
-    <row r="151" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="23">
         <v>150</v>
       </c>
       <c r="B151" s="45" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C151" s="33" t="s">
         <v>32</v>
@@ -6963,19 +6963,19 @@
       </c>
       <c r="G151" s="55"/>
       <c r="H151" s="55" t="s">
+        <v>251</v>
+      </c>
+      <c r="I151" s="55" t="s">
         <v>252</v>
       </c>
-      <c r="I151" s="55" t="s">
-        <v>253</v>
-      </c>
       <c r="J151" s="48"/>
     </row>
-    <row r="152" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" ht="112.2" x14ac:dyDescent="0.3">
       <c r="A152" s="23">
         <v>151</v>
       </c>
       <c r="B152" s="45" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C152" s="33" t="s">
         <v>69</v>
@@ -6992,15 +6992,15 @@
       <c r="G152" s="55"/>
       <c r="H152" s="55"/>
       <c r="I152" s="55" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10" ht="112.5" x14ac:dyDescent="0.25">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" ht="102" x14ac:dyDescent="0.3">
       <c r="A153" s="23">
         <v>152</v>
       </c>
       <c r="B153" s="45" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C153" s="33" t="s">
         <v>70</v>
@@ -7017,15 +7017,15 @@
       <c r="G153" s="55"/>
       <c r="H153" s="55"/>
       <c r="I153" s="55" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="154" spans="1:10" ht="157.5" x14ac:dyDescent="0.25">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" ht="132.6" x14ac:dyDescent="0.3">
       <c r="A154" s="23">
         <v>153</v>
       </c>
       <c r="B154" s="45" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C154" s="33" t="s">
         <v>69</v>
@@ -7042,15 +7042,15 @@
       <c r="G154" s="55"/>
       <c r="H154" s="55"/>
       <c r="I154" s="55" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="155" spans="1:10" ht="202.5" x14ac:dyDescent="0.25">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" ht="163.19999999999999" x14ac:dyDescent="0.3">
       <c r="A155" s="23">
         <v>154</v>
       </c>
       <c r="B155" s="45" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C155" s="33" t="s">
         <v>69</v>
@@ -7067,15 +7067,15 @@
       <c r="G155" s="55"/>
       <c r="H155" s="55"/>
       <c r="I155" s="55" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="156" spans="1:10" ht="146.25" x14ac:dyDescent="0.25">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" ht="132.6" x14ac:dyDescent="0.3">
       <c r="A156" s="23">
         <v>155</v>
       </c>
       <c r="B156" s="60" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C156" s="33" t="s">
         <v>69</v>
@@ -7092,15 +7092,15 @@
       <c r="G156" s="55"/>
       <c r="H156" s="55"/>
       <c r="I156" s="55" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="157" spans="1:10" ht="168.75" x14ac:dyDescent="0.25">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" ht="142.80000000000001" x14ac:dyDescent="0.3">
       <c r="A157" s="23">
         <v>156</v>
       </c>
       <c r="B157" s="60" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C157" s="33" t="s">
         <v>69</v>
@@ -7117,15 +7117,15 @@
       <c r="G157" s="55"/>
       <c r="H157" s="55"/>
       <c r="I157" s="55" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="158" spans="1:10" ht="101.25" x14ac:dyDescent="0.25">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" ht="91.8" x14ac:dyDescent="0.3">
       <c r="A158" s="23">
         <v>157</v>
       </c>
       <c r="B158" s="45" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C158" s="33" t="s">
         <v>70</v>
@@ -7142,15 +7142,15 @@
       <c r="G158" s="55"/>
       <c r="H158" s="55"/>
       <c r="I158" s="55" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="159" spans="1:10" ht="168.75" x14ac:dyDescent="0.25">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" ht="142.80000000000001" x14ac:dyDescent="0.3">
       <c r="A159" s="23">
         <v>158</v>
       </c>
       <c r="B159" s="45" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C159" s="33" t="s">
         <v>32</v>
@@ -7167,15 +7167,15 @@
       <c r="G159" s="55"/>
       <c r="H159" s="55"/>
       <c r="I159" s="55" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="160" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" ht="112.2" x14ac:dyDescent="0.3">
       <c r="A160" s="23">
         <v>159</v>
       </c>
       <c r="B160" s="60" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C160" s="33" t="s">
         <v>69</v>
@@ -7192,15 +7192,15 @@
       <c r="G160" s="55"/>
       <c r="H160" s="55"/>
       <c r="I160" s="55" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="161" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" ht="81.599999999999994" x14ac:dyDescent="0.3">
       <c r="A161" s="23">
         <v>160</v>
       </c>
       <c r="B161" s="45" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C161" s="33" t="s">
         <v>69</v>
@@ -7217,15 +7217,15 @@
       <c r="G161" s="55"/>
       <c r="H161" s="55"/>
       <c r="I161" s="55" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="162" spans="1:9" ht="123.75" x14ac:dyDescent="0.25">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" ht="112.2" x14ac:dyDescent="0.3">
       <c r="A162" s="23">
         <v>161</v>
       </c>
       <c r="B162" s="45" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C162" s="33" t="s">
         <v>69</v>
@@ -7242,15 +7242,15 @@
       <c r="G162" s="55"/>
       <c r="H162" s="55"/>
       <c r="I162" s="55" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="163" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" ht="81.599999999999994" x14ac:dyDescent="0.3">
       <c r="A163" s="23">
         <v>162</v>
       </c>
       <c r="B163" s="45" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C163" s="33" t="s">
         <v>69</v>
@@ -7267,15 +7267,15 @@
       <c r="G163" s="55"/>
       <c r="H163" s="55"/>
       <c r="I163" s="55" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="164" spans="1:9" ht="157.5" x14ac:dyDescent="0.25">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" ht="122.4" x14ac:dyDescent="0.3">
       <c r="A164" s="23">
         <v>163</v>
       </c>
       <c r="B164" s="45" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C164" s="33" t="s">
         <v>69</v>
@@ -7292,15 +7292,15 @@
       <c r="G164" s="55"/>
       <c r="H164" s="55"/>
       <c r="I164" s="55" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="165" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" ht="81.599999999999994" x14ac:dyDescent="0.3">
       <c r="A165" s="23">
         <v>164</v>
       </c>
       <c r="B165" s="45" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C165" s="33" t="s">
         <v>69</v>
@@ -7317,15 +7317,15 @@
       <c r="G165" s="55"/>
       <c r="H165" s="55"/>
       <c r="I165" s="55" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="166" spans="1:9" ht="123.75" x14ac:dyDescent="0.25">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" ht="102" x14ac:dyDescent="0.3">
       <c r="A166" s="23">
         <v>165</v>
       </c>
       <c r="B166" s="45" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C166" s="33" t="s">
         <v>69</v>
@@ -7342,15 +7342,15 @@
       <c r="G166" s="55"/>
       <c r="H166" s="55"/>
       <c r="I166" s="55" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="167" spans="1:9" ht="123.75" x14ac:dyDescent="0.25">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" ht="112.2" x14ac:dyDescent="0.3">
       <c r="A167" s="23">
         <v>166</v>
       </c>
       <c r="B167" s="45" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C167" s="33" t="s">
         <v>69</v>
@@ -7367,15 +7367,15 @@
       <c r="G167" s="55"/>
       <c r="H167" s="55"/>
       <c r="I167" s="55" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="168" spans="1:9" ht="101.25" x14ac:dyDescent="0.25">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" ht="81.599999999999994" x14ac:dyDescent="0.3">
       <c r="A168" s="23">
         <v>167</v>
       </c>
       <c r="B168" s="45" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C168" s="33" t="s">
         <v>69</v>
@@ -7392,15 +7392,15 @@
       <c r="G168" s="55"/>
       <c r="H168" s="55"/>
       <c r="I168" s="55" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="169" spans="1:9" ht="135" x14ac:dyDescent="0.25">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" ht="112.2" x14ac:dyDescent="0.3">
       <c r="A169" s="23">
         <v>168</v>
       </c>
       <c r="B169" s="45" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C169" s="33" t="s">
         <v>69</v>
@@ -7417,15 +7417,15 @@
       <c r="G169" s="55"/>
       <c r="H169" s="55"/>
       <c r="I169" s="55" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="170" spans="1:9" ht="135" x14ac:dyDescent="0.25">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" ht="112.2" x14ac:dyDescent="0.3">
       <c r="A170" s="23">
         <v>169</v>
       </c>
       <c r="B170" s="45" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C170" s="33" t="s">
         <v>69</v>
@@ -7442,15 +7442,15 @@
       <c r="G170" s="55"/>
       <c r="H170" s="55"/>
       <c r="I170" s="55" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="171" spans="1:9" ht="101.25" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" ht="81.599999999999994" x14ac:dyDescent="0.3">
       <c r="A171" s="23">
         <v>170</v>
       </c>
       <c r="B171" s="45" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C171" s="33" t="s">
         <v>69</v>
@@ -7467,7 +7467,7 @@
       <c r="G171" s="55"/>
       <c r="H171" s="55"/>
       <c r="I171" s="55" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
   </sheetData>
@@ -7479,20 +7479,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3D11E14-B088-4037-AA65-FC43834A326E}">
   <dimension ref="A1:H29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" customWidth="1"/>
-    <col min="2" max="2" width="53.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
-    <col min="5" max="5" width="3.28515625" customWidth="1"/>
-    <col min="6" max="6" width="21.28515625" customWidth="1"/>
-    <col min="7" max="7" width="25.7109375" customWidth="1"/>
-    <col min="8" max="8" width="34.85546875" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" customWidth="1"/>
+    <col min="2" max="2" width="53.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" customWidth="1"/>
+    <col min="5" max="5" width="3.33203125" customWidth="1"/>
+    <col min="6" max="6" width="21.33203125" customWidth="1"/>
+    <col min="7" max="7" width="25.6640625" customWidth="1"/>
+    <col min="8" max="8" width="34.88671875" customWidth="1"/>
     <col min="9" max="9" width="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>68</v>
       </c>
@@ -7500,7 +7500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -7508,7 +7508,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -7516,7 +7516,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
@@ -7524,7 +7524,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>8</v>
       </c>
@@ -7532,7 +7532,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>9</v>
       </c>
@@ -7540,7 +7540,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
@@ -7548,7 +7548,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>11</v>
       </c>
@@ -7556,7 +7556,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>12</v>
       </c>
@@ -7564,7 +7564,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>13</v>
       </c>
@@ -7572,27 +7572,27 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
       <c r="B13" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
       <c r="B14" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
       <c r="B15" s="2"/>
     </row>
-    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
       <c r="B16" s="2"/>
     </row>
-    <row r="18" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C18" s="8" t="s">
         <v>110</v>
       </c>
@@ -7600,25 +7600,25 @@
         <v>110</v>
       </c>
     </row>
-    <row r="19" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C19" s="7" t="s">
         <v>111</v>
       </c>
       <c r="D19" s="1"/>
     </row>
-    <row r="20" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C20" s="7" t="s">
         <v>112</v>
       </c>
       <c r="D20" s="1"/>
     </row>
-    <row r="21" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C21" s="7" t="s">
         <v>119</v>
       </c>
       <c r="D21" s="1"/>
     </row>
-    <row r="23" spans="3:8" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:8" ht="18" x14ac:dyDescent="0.3">
       <c r="F23" s="9" t="s">
         <v>109</v>
       </c>
@@ -7629,7 +7629,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="24" spans="3:8" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:8" ht="18" x14ac:dyDescent="0.3">
       <c r="F24" s="10" t="s">
         <v>26</v>
       </c>
@@ -7640,14 +7640,14 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="3:8" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:8" ht="18" x14ac:dyDescent="0.3">
       <c r="F25" s="10" t="s">
         <v>27</v>
       </c>
       <c r="G25" s="11"/>
       <c r="H25" s="11"/>
     </row>
-    <row r="26" spans="3:8" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:8" ht="18" x14ac:dyDescent="0.3">
       <c r="F26" s="10" t="s">
         <v>28</v>
       </c>
@@ -7656,7 +7656,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="27" spans="3:8" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:8" ht="18" x14ac:dyDescent="0.3">
       <c r="F27" s="10" t="s">
         <v>60</v>
       </c>
@@ -7667,14 +7667,14 @@
         <v>120</v>
       </c>
     </row>
-    <row r="28" spans="3:8" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:8" ht="18" x14ac:dyDescent="0.3">
       <c r="F28" s="10" t="s">
         <v>113</v>
       </c>
       <c r="G28" s="11"/>
       <c r="H28" s="11"/>
     </row>
-    <row r="29" spans="3:8" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:8" ht="18" x14ac:dyDescent="0.3">
       <c r="F29" s="10" t="s">
         <v>118</v>
       </c>
